--- a/quotes/הצעת-מחיר-חודשית-תכנית-חוסן.xlsx
+++ b/quotes/הצעת-מחיר-חודשית-תכנית-חוסן.xlsx
@@ -1153,9 +1153,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="118">
   <si>
     <t xml:space="preserve">איך משתמשים בקובץ – תכנית חוסן</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חשוב – הגיליונות נעולים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אפשר לכתוב רק בתאים הצבעוניים (צהוב בהגדרות, שמנת בהצעה). כל השאר – נוסחאות – נעול, כך שאי אפשר למחוק אותן בטעות. אם ממש צריך לשנות משהו אחר: סקירה ← ביטול הגנת גיליון (אין סיסמה).</t>
   </si>
   <si>
     <t xml:space="preserve">1. פעם אחת</t>
@@ -1167,7 +1173,7 @@
     <t xml:space="preserve">2. אוגוסט–ספטמבר 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">גיליון אחד ל־19/08–30/09/2026, עם כל ימי שלישי ורביעי בתקופה. מוחקים (Delete) תאריך של מפגש שלא היה, מתקנים תאריך שהשתנה, ובשורות הריקות בסוף מוסיפים מפגשים נוספים.</t>
+    <t xml:space="preserve">גיליון אחד ל־19/08–30/09/2026, עם כל ימי שלישי ורביעי בתקופה. מוחקים (Delete) את התאריך של מפגש שלא היה – השורה מתרוקנת ולא מחויבת. מתקנים תאריך שהשתנה, ובשורות הריקות בסוף מוסיפים מפגשים נוספים.</t>
   </si>
   <si>
     <t xml:space="preserve">3. מאוקטובר – בסוף כל חודש</t>
@@ -1917,9 +1923,9 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -1929,21 +1935,21 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
@@ -1965,13 +1971,13 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
@@ -1993,17 +1999,17 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
@@ -2017,13 +2023,13 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -2077,9 +2083,9 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
@@ -2356,7 +2362,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:C19"/>
+  <dimension ref="B1:C20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2441,41 +2447,49 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+    <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="C12" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5"/>
-      <c r="C14" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="7"/>
-      <c r="C15" s="8" t="s">
+      <c r="B14" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="5"/>
+      <c r="C15" s="6" t="s">
         <v>22</v>
       </c>
     </row>
+    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="7"/>
+      <c r="C16" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="9" t="s">
+      <c r="B18" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="11" t="n">
         <v>850</v>
       </c>
     </row>
@@ -2512,7 +2526,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2554,14 +2568,14 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
       <c r="G4" s="26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H4" s="26"/>
       <c r="I4" s="26"/>
@@ -2571,7 +2585,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="27"/>
       <c r="C5" s="28" t="str">
@@ -2581,7 +2595,7 @@
       <c r="D5" s="28"/>
       <c r="E5" s="28"/>
       <c r="G5" s="27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H5" s="27"/>
       <c r="I5" s="28" t="str">
@@ -2594,7 +2608,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="27"/>
       <c r="C6" s="28" t="str">
@@ -2604,7 +2618,7 @@
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="G6" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H6" s="27"/>
       <c r="I6" s="28" t="str">
@@ -2617,7 +2631,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B7" s="27"/>
       <c r="C7" s="28" t="str">
@@ -2627,7 +2641,7 @@
       <c r="D7" s="28"/>
       <c r="E7" s="28"/>
       <c r="G7" s="27" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H7" s="27"/>
       <c r="I7" s="28" t="str">
@@ -2640,7 +2654,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="27"/>
       <c r="C8" s="28" t="str">
@@ -2652,7 +2666,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="27"/>
       <c r="C9" s="28" t="str">
@@ -2665,7 +2679,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B11" s="27"/>
       <c r="C11" s="28" t="str">
@@ -2675,7 +2689,7 @@
       <c r="D11" s="28"/>
       <c r="E11" s="28"/>
       <c r="G11" s="27" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H11" s="27"/>
       <c r="I11" s="57" t="n">
@@ -2687,7 +2701,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B12" s="27"/>
       <c r="C12" s="58" t="n">
@@ -2697,7 +2711,7 @@
       <c r="D12" s="58"/>
       <c r="E12" s="58"/>
       <c r="G12" s="27" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H12" s="27"/>
       <c r="I12" s="28" t="str">
@@ -2723,46 +2737,46 @@
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
       <c r="K13" s="32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L13" s="32"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K14" s="34" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L14" s="34" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2779,7 +2793,7 @@
         <v>רביעי</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E15" s="38" t="n">
         <f aca="false">IF(B15="","",הגדרות!$C$28)</f>
@@ -2827,7 +2841,7 @@
         <v>רביעי</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E16" s="38" t="n">
         <f aca="false">IF(B16="","",הגדרות!$C$28)</f>
@@ -2875,7 +2889,7 @@
         <v>רביעי</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E17" s="38" t="n">
         <f aca="false">IF(B17="","",הגדרות!$C$28)</f>
@@ -2923,7 +2937,7 @@
         <v>רביעי</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E18" s="38" t="n">
         <f aca="false">IF(B18="","",הגדרות!$C$28)</f>
@@ -2971,7 +2985,7 @@
         <v/>
       </c>
       <c r="D19" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E19" s="38" t="str">
         <f aca="false">IF(B19="","",הגדרות!$C$28)</f>
@@ -3019,7 +3033,7 @@
         <v/>
       </c>
       <c r="D20" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E20" s="38" t="str">
         <f aca="false">IF(B20="","",הגדרות!$C$28)</f>
@@ -3067,7 +3081,7 @@
         <v/>
       </c>
       <c r="D21" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E21" s="38" t="str">
         <f aca="false">IF(B21="","",הגדרות!$C$28)</f>
@@ -3115,7 +3129,7 @@
         <v/>
       </c>
       <c r="D22" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E22" s="38" t="str">
         <f aca="false">IF(B22="","",הגדרות!$C$28)</f>
@@ -3163,7 +3177,7 @@
         <v/>
       </c>
       <c r="D23" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E23" s="38" t="str">
         <f aca="false">IF(B23="","",הגדרות!$C$28)</f>
@@ -3211,7 +3225,7 @@
         <v/>
       </c>
       <c r="D24" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E24" s="38" t="str">
         <f aca="false">IF(B24="","",הגדרות!$C$28)</f>
@@ -3247,7 +3261,7 @@
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="45" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B25" s="45"/>
       <c r="C25" s="45"/>
@@ -3278,7 +3292,7 @@
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -3294,7 +3308,7 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
@@ -3349,7 +3363,7 @@
       <c r="F30" s="51"/>
       <c r="G30" s="51"/>
       <c r="H30" s="50" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I30" s="50"/>
       <c r="J30" s="50"/>
@@ -3371,7 +3385,7 @@
       <c r="F31" s="51"/>
       <c r="G31" s="51"/>
       <c r="H31" s="52" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I31" s="52"/>
       <c r="J31" s="52"/>
@@ -3416,7 +3430,7 @@
       <c r="F33" s="51"/>
       <c r="G33" s="51"/>
       <c r="H33" s="53" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I33" s="53"/>
       <c r="J33" s="53"/>
@@ -3440,7 +3454,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B35" s="49"/>
       <c r="C35" s="49"/>
@@ -3532,7 +3546,7 @@
       <c r="D42" s="55"/>
       <c r="E42" s="55"/>
       <c r="H42" s="55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I42" s="55"/>
       <c r="J42" s="55"/>
@@ -3540,6 +3554,7 @@
       <c r="L42" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="52">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
@@ -3654,7 +3669,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -3696,14 +3711,14 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
       <c r="G4" s="26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H4" s="26"/>
       <c r="I4" s="26"/>
@@ -3713,7 +3728,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="27"/>
       <c r="C5" s="28" t="str">
@@ -3723,7 +3738,7 @@
       <c r="D5" s="28"/>
       <c r="E5" s="28"/>
       <c r="G5" s="27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H5" s="27"/>
       <c r="I5" s="28" t="str">
@@ -3736,7 +3751,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="27"/>
       <c r="C6" s="28" t="str">
@@ -3746,7 +3761,7 @@
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="G6" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H6" s="27"/>
       <c r="I6" s="28" t="str">
@@ -3759,7 +3774,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B7" s="27"/>
       <c r="C7" s="28" t="str">
@@ -3769,7 +3784,7 @@
       <c r="D7" s="28"/>
       <c r="E7" s="28"/>
       <c r="G7" s="27" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H7" s="27"/>
       <c r="I7" s="28" t="str">
@@ -3782,7 +3797,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="27"/>
       <c r="C8" s="28" t="str">
@@ -3794,7 +3809,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="27"/>
       <c r="C9" s="28" t="str">
@@ -3807,7 +3822,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B11" s="27"/>
       <c r="C11" s="28" t="str">
@@ -3817,7 +3832,7 @@
       <c r="D11" s="28"/>
       <c r="E11" s="28"/>
       <c r="G11" s="27" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H11" s="27"/>
       <c r="I11" s="57" t="n">
@@ -3829,7 +3844,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B12" s="27"/>
       <c r="C12" s="58" t="n">
@@ -3839,7 +3854,7 @@
       <c r="D12" s="58"/>
       <c r="E12" s="58"/>
       <c r="G12" s="27" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H12" s="27"/>
       <c r="I12" s="28" t="str">
@@ -3865,46 +3880,46 @@
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
       <c r="K13" s="32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L13" s="32"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K14" s="34" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L14" s="34" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3921,7 +3936,7 @@
         <v>רביעי</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E15" s="38" t="n">
         <f aca="false">IF(B15="","",הגדרות!$C$28)</f>
@@ -3969,7 +3984,7 @@
         <v>רביעי</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E16" s="38" t="n">
         <f aca="false">IF(B16="","",הגדרות!$C$28)</f>
@@ -4017,7 +4032,7 @@
         <v>רביעי</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E17" s="38" t="n">
         <f aca="false">IF(B17="","",הגדרות!$C$28)</f>
@@ -4065,7 +4080,7 @@
         <v>רביעי</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E18" s="38" t="n">
         <f aca="false">IF(B18="","",הגדרות!$C$28)</f>
@@ -4113,7 +4128,7 @@
         <v/>
       </c>
       <c r="D19" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E19" s="38" t="str">
         <f aca="false">IF(B19="","",הגדרות!$C$28)</f>
@@ -4161,7 +4176,7 @@
         <v/>
       </c>
       <c r="D20" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E20" s="38" t="str">
         <f aca="false">IF(B20="","",הגדרות!$C$28)</f>
@@ -4209,7 +4224,7 @@
         <v/>
       </c>
       <c r="D21" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E21" s="38" t="str">
         <f aca="false">IF(B21="","",הגדרות!$C$28)</f>
@@ -4257,7 +4272,7 @@
         <v/>
       </c>
       <c r="D22" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E22" s="38" t="str">
         <f aca="false">IF(B22="","",הגדרות!$C$28)</f>
@@ -4305,7 +4320,7 @@
         <v/>
       </c>
       <c r="D23" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E23" s="38" t="str">
         <f aca="false">IF(B23="","",הגדרות!$C$28)</f>
@@ -4353,7 +4368,7 @@
         <v/>
       </c>
       <c r="D24" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E24" s="38" t="str">
         <f aca="false">IF(B24="","",הגדרות!$C$28)</f>
@@ -4389,7 +4404,7 @@
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="45" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B25" s="45"/>
       <c r="C25" s="45"/>
@@ -4420,7 +4435,7 @@
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -4436,7 +4451,7 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
@@ -4491,7 +4506,7 @@
       <c r="F30" s="51"/>
       <c r="G30" s="51"/>
       <c r="H30" s="50" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I30" s="50"/>
       <c r="J30" s="50"/>
@@ -4513,7 +4528,7 @@
       <c r="F31" s="51"/>
       <c r="G31" s="51"/>
       <c r="H31" s="52" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I31" s="52"/>
       <c r="J31" s="52"/>
@@ -4558,7 +4573,7 @@
       <c r="F33" s="51"/>
       <c r="G33" s="51"/>
       <c r="H33" s="53" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I33" s="53"/>
       <c r="J33" s="53"/>
@@ -4582,7 +4597,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B35" s="49"/>
       <c r="C35" s="49"/>
@@ -4674,7 +4689,7 @@
       <c r="D42" s="55"/>
       <c r="E42" s="55"/>
       <c r="H42" s="55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I42" s="55"/>
       <c r="J42" s="55"/>
@@ -4682,6 +4697,7 @@
       <c r="L42" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="52">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
@@ -4796,7 +4812,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -4838,14 +4854,14 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
       <c r="G4" s="26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H4" s="26"/>
       <c r="I4" s="26"/>
@@ -4855,7 +4871,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="27"/>
       <c r="C5" s="28" t="str">
@@ -4865,7 +4881,7 @@
       <c r="D5" s="28"/>
       <c r="E5" s="28"/>
       <c r="G5" s="27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H5" s="27"/>
       <c r="I5" s="28" t="str">
@@ -4878,7 +4894,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="27"/>
       <c r="C6" s="28" t="str">
@@ -4888,7 +4904,7 @@
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="G6" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H6" s="27"/>
       <c r="I6" s="28" t="str">
@@ -4901,7 +4917,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B7" s="27"/>
       <c r="C7" s="28" t="str">
@@ -4911,7 +4927,7 @@
       <c r="D7" s="28"/>
       <c r="E7" s="28"/>
       <c r="G7" s="27" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H7" s="27"/>
       <c r="I7" s="28" t="str">
@@ -4924,7 +4940,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="27"/>
       <c r="C8" s="28" t="str">
@@ -4936,7 +4952,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="27"/>
       <c r="C9" s="28" t="str">
@@ -4949,7 +4965,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B11" s="27"/>
       <c r="C11" s="28" t="str">
@@ -4959,7 +4975,7 @@
       <c r="D11" s="28"/>
       <c r="E11" s="28"/>
       <c r="G11" s="27" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H11" s="27"/>
       <c r="I11" s="57" t="n">
@@ -4971,7 +4987,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B12" s="27"/>
       <c r="C12" s="58" t="n">
@@ -4981,7 +4997,7 @@
       <c r="D12" s="58"/>
       <c r="E12" s="58"/>
       <c r="G12" s="27" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H12" s="27"/>
       <c r="I12" s="28" t="str">
@@ -5007,46 +5023,46 @@
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
       <c r="K13" s="32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L13" s="32"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K14" s="34" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L14" s="34" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5063,7 +5079,7 @@
         <v>רביעי</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E15" s="38" t="n">
         <f aca="false">IF(B15="","",הגדרות!$C$28)</f>
@@ -5111,7 +5127,7 @@
         <v>רביעי</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E16" s="38" t="n">
         <f aca="false">IF(B16="","",הגדרות!$C$28)</f>
@@ -5159,7 +5175,7 @@
         <v>רביעי</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E17" s="38" t="n">
         <f aca="false">IF(B17="","",הגדרות!$C$28)</f>
@@ -5207,7 +5223,7 @@
         <v>רביעי</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E18" s="38" t="n">
         <f aca="false">IF(B18="","",הגדרות!$C$28)</f>
@@ -5255,7 +5271,7 @@
         <v>רביעי</v>
       </c>
       <c r="D19" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E19" s="38" t="n">
         <f aca="false">IF(B19="","",הגדרות!$C$28)</f>
@@ -5303,7 +5319,7 @@
         <v/>
       </c>
       <c r="D20" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E20" s="38" t="str">
         <f aca="false">IF(B20="","",הגדרות!$C$28)</f>
@@ -5351,7 +5367,7 @@
         <v/>
       </c>
       <c r="D21" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E21" s="38" t="str">
         <f aca="false">IF(B21="","",הגדרות!$C$28)</f>
@@ -5399,7 +5415,7 @@
         <v/>
       </c>
       <c r="D22" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E22" s="38" t="str">
         <f aca="false">IF(B22="","",הגדרות!$C$28)</f>
@@ -5447,7 +5463,7 @@
         <v/>
       </c>
       <c r="D23" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E23" s="38" t="str">
         <f aca="false">IF(B23="","",הגדרות!$C$28)</f>
@@ -5495,7 +5511,7 @@
         <v/>
       </c>
       <c r="D24" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E24" s="38" t="str">
         <f aca="false">IF(B24="","",הגדרות!$C$28)</f>
@@ -5531,7 +5547,7 @@
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="45" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B25" s="45"/>
       <c r="C25" s="45"/>
@@ -5562,7 +5578,7 @@
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -5578,7 +5594,7 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
@@ -5633,7 +5649,7 @@
       <c r="F30" s="51"/>
       <c r="G30" s="51"/>
       <c r="H30" s="50" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I30" s="50"/>
       <c r="J30" s="50"/>
@@ -5655,7 +5671,7 @@
       <c r="F31" s="51"/>
       <c r="G31" s="51"/>
       <c r="H31" s="52" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I31" s="52"/>
       <c r="J31" s="52"/>
@@ -5700,7 +5716,7 @@
       <c r="F33" s="51"/>
       <c r="G33" s="51"/>
       <c r="H33" s="53" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I33" s="53"/>
       <c r="J33" s="53"/>
@@ -5724,7 +5740,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B35" s="49"/>
       <c r="C35" s="49"/>
@@ -5816,7 +5832,7 @@
       <c r="D42" s="55"/>
       <c r="E42" s="55"/>
       <c r="H42" s="55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I42" s="55"/>
       <c r="J42" s="55"/>
@@ -5824,6 +5840,7 @@
       <c r="L42" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="52">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
@@ -5938,7 +5955,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -5980,14 +5997,14 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
       <c r="G4" s="26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H4" s="26"/>
       <c r="I4" s="26"/>
@@ -5997,7 +6014,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="27"/>
       <c r="C5" s="28" t="str">
@@ -6007,7 +6024,7 @@
       <c r="D5" s="28"/>
       <c r="E5" s="28"/>
       <c r="G5" s="27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H5" s="27"/>
       <c r="I5" s="28" t="str">
@@ -6020,7 +6037,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="27"/>
       <c r="C6" s="28" t="str">
@@ -6030,7 +6047,7 @@
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="G6" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H6" s="27"/>
       <c r="I6" s="28" t="str">
@@ -6043,7 +6060,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B7" s="27"/>
       <c r="C7" s="28" t="str">
@@ -6053,7 +6070,7 @@
       <c r="D7" s="28"/>
       <c r="E7" s="28"/>
       <c r="G7" s="27" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H7" s="27"/>
       <c r="I7" s="28" t="str">
@@ -6066,7 +6083,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="27"/>
       <c r="C8" s="28" t="str">
@@ -6078,7 +6095,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="27"/>
       <c r="C9" s="28" t="str">
@@ -6091,7 +6108,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B11" s="27"/>
       <c r="C11" s="28" t="str">
@@ -6101,7 +6118,7 @@
       <c r="D11" s="28"/>
       <c r="E11" s="28"/>
       <c r="G11" s="27" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H11" s="27"/>
       <c r="I11" s="57" t="n">
@@ -6113,7 +6130,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B12" s="27"/>
       <c r="C12" s="58" t="n">
@@ -6123,7 +6140,7 @@
       <c r="D12" s="58"/>
       <c r="E12" s="58"/>
       <c r="G12" s="27" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H12" s="27"/>
       <c r="I12" s="28" t="str">
@@ -6149,46 +6166,46 @@
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
       <c r="K13" s="32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L13" s="32"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K14" s="34" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L14" s="34" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6205,7 +6222,7 @@
         <v>רביעי</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E15" s="38" t="n">
         <f aca="false">IF(B15="","",הגדרות!$C$28)</f>
@@ -6253,7 +6270,7 @@
         <v>רביעי</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E16" s="38" t="n">
         <f aca="false">IF(B16="","",הגדרות!$C$28)</f>
@@ -6301,7 +6318,7 @@
         <v>רביעי</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E17" s="38" t="n">
         <f aca="false">IF(B17="","",הגדרות!$C$28)</f>
@@ -6349,7 +6366,7 @@
         <v>רביעי</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E18" s="38" t="n">
         <f aca="false">IF(B18="","",הגדרות!$C$28)</f>
@@ -6397,7 +6414,7 @@
         <v/>
       </c>
       <c r="D19" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E19" s="38" t="str">
         <f aca="false">IF(B19="","",הגדרות!$C$28)</f>
@@ -6445,7 +6462,7 @@
         <v/>
       </c>
       <c r="D20" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E20" s="38" t="str">
         <f aca="false">IF(B20="","",הגדרות!$C$28)</f>
@@ -6493,7 +6510,7 @@
         <v/>
       </c>
       <c r="D21" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E21" s="38" t="str">
         <f aca="false">IF(B21="","",הגדרות!$C$28)</f>
@@ -6541,7 +6558,7 @@
         <v/>
       </c>
       <c r="D22" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E22" s="38" t="str">
         <f aca="false">IF(B22="","",הגדרות!$C$28)</f>
@@ -6589,7 +6606,7 @@
         <v/>
       </c>
       <c r="D23" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E23" s="38" t="str">
         <f aca="false">IF(B23="","",הגדרות!$C$28)</f>
@@ -6637,7 +6654,7 @@
         <v/>
       </c>
       <c r="D24" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E24" s="38" t="str">
         <f aca="false">IF(B24="","",הגדרות!$C$28)</f>
@@ -6673,7 +6690,7 @@
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="45" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B25" s="45"/>
       <c r="C25" s="45"/>
@@ -6704,7 +6721,7 @@
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -6720,7 +6737,7 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
@@ -6775,7 +6792,7 @@
       <c r="F30" s="51"/>
       <c r="G30" s="51"/>
       <c r="H30" s="50" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I30" s="50"/>
       <c r="J30" s="50"/>
@@ -6797,7 +6814,7 @@
       <c r="F31" s="51"/>
       <c r="G31" s="51"/>
       <c r="H31" s="52" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I31" s="52"/>
       <c r="J31" s="52"/>
@@ -6842,7 +6859,7 @@
       <c r="F33" s="51"/>
       <c r="G33" s="51"/>
       <c r="H33" s="53" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I33" s="53"/>
       <c r="J33" s="53"/>
@@ -6866,7 +6883,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B35" s="49"/>
       <c r="C35" s="49"/>
@@ -6958,7 +6975,7 @@
       <c r="D42" s="55"/>
       <c r="E42" s="55"/>
       <c r="H42" s="55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I42" s="55"/>
       <c r="J42" s="55"/>
@@ -6966,6 +6983,7 @@
       <c r="L42" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="52">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
@@ -7080,7 +7098,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -7122,14 +7140,14 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
       <c r="G4" s="26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H4" s="26"/>
       <c r="I4" s="26"/>
@@ -7139,7 +7157,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="27"/>
       <c r="C5" s="28" t="str">
@@ -7149,7 +7167,7 @@
       <c r="D5" s="28"/>
       <c r="E5" s="28"/>
       <c r="G5" s="27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H5" s="27"/>
       <c r="I5" s="28" t="str">
@@ -7162,7 +7180,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="27"/>
       <c r="C6" s="28" t="str">
@@ -7172,7 +7190,7 @@
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="G6" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H6" s="27"/>
       <c r="I6" s="28" t="str">
@@ -7185,7 +7203,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B7" s="27"/>
       <c r="C7" s="28" t="str">
@@ -7195,7 +7213,7 @@
       <c r="D7" s="28"/>
       <c r="E7" s="28"/>
       <c r="G7" s="27" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H7" s="27"/>
       <c r="I7" s="28" t="str">
@@ -7208,7 +7226,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="27"/>
       <c r="C8" s="28" t="str">
@@ -7220,7 +7238,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="27"/>
       <c r="C9" s="28" t="str">
@@ -7233,7 +7251,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B11" s="27"/>
       <c r="C11" s="28" t="str">
@@ -7243,7 +7261,7 @@
       <c r="D11" s="28"/>
       <c r="E11" s="28"/>
       <c r="G11" s="27" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H11" s="27"/>
       <c r="I11" s="57" t="n">
@@ -7255,7 +7273,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B12" s="27"/>
       <c r="C12" s="58" t="n">
@@ -7265,7 +7283,7 @@
       <c r="D12" s="58"/>
       <c r="E12" s="58"/>
       <c r="G12" s="27" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H12" s="27"/>
       <c r="I12" s="28" t="str">
@@ -7291,46 +7309,46 @@
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
       <c r="K13" s="32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L13" s="32"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K14" s="34" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L14" s="34" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7347,7 +7365,7 @@
         <v>רביעי</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E15" s="38" t="n">
         <f aca="false">IF(B15="","",הגדרות!$C$28)</f>
@@ -7395,7 +7413,7 @@
         <v>רביעי</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E16" s="38" t="n">
         <f aca="false">IF(B16="","",הגדרות!$C$28)</f>
@@ -7443,7 +7461,7 @@
         <v>רביעי</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E17" s="38" t="n">
         <f aca="false">IF(B17="","",הגדרות!$C$28)</f>
@@ -7491,7 +7509,7 @@
         <v>רביעי</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E18" s="38" t="n">
         <f aca="false">IF(B18="","",הגדרות!$C$28)</f>
@@ -7539,7 +7557,7 @@
         <v/>
       </c>
       <c r="D19" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E19" s="38" t="str">
         <f aca="false">IF(B19="","",הגדרות!$C$28)</f>
@@ -7587,7 +7605,7 @@
         <v/>
       </c>
       <c r="D20" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E20" s="38" t="str">
         <f aca="false">IF(B20="","",הגדרות!$C$28)</f>
@@ -7635,7 +7653,7 @@
         <v/>
       </c>
       <c r="D21" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E21" s="38" t="str">
         <f aca="false">IF(B21="","",הגדרות!$C$28)</f>
@@ -7683,7 +7701,7 @@
         <v/>
       </c>
       <c r="D22" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E22" s="38" t="str">
         <f aca="false">IF(B22="","",הגדרות!$C$28)</f>
@@ -7731,7 +7749,7 @@
         <v/>
       </c>
       <c r="D23" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E23" s="38" t="str">
         <f aca="false">IF(B23="","",הגדרות!$C$28)</f>
@@ -7779,7 +7797,7 @@
         <v/>
       </c>
       <c r="D24" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E24" s="38" t="str">
         <f aca="false">IF(B24="","",הגדרות!$C$28)</f>
@@ -7815,7 +7833,7 @@
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="45" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B25" s="45"/>
       <c r="C25" s="45"/>
@@ -7846,7 +7864,7 @@
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -7862,7 +7880,7 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
@@ -7917,7 +7935,7 @@
       <c r="F30" s="51"/>
       <c r="G30" s="51"/>
       <c r="H30" s="50" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I30" s="50"/>
       <c r="J30" s="50"/>
@@ -7939,7 +7957,7 @@
       <c r="F31" s="51"/>
       <c r="G31" s="51"/>
       <c r="H31" s="52" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I31" s="52"/>
       <c r="J31" s="52"/>
@@ -7984,7 +8002,7 @@
       <c r="F33" s="51"/>
       <c r="G33" s="51"/>
       <c r="H33" s="53" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I33" s="53"/>
       <c r="J33" s="53"/>
@@ -8008,7 +8026,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B35" s="49"/>
       <c r="C35" s="49"/>
@@ -8100,7 +8118,7 @@
       <c r="D42" s="55"/>
       <c r="E42" s="55"/>
       <c r="H42" s="55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I42" s="55"/>
       <c r="J42" s="55"/>
@@ -8108,6 +8126,7 @@
       <c r="L42" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="52">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
@@ -8222,7 +8241,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -8264,14 +8283,14 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
       <c r="G4" s="26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H4" s="26"/>
       <c r="I4" s="26"/>
@@ -8281,7 +8300,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="27"/>
       <c r="C5" s="28" t="str">
@@ -8291,7 +8310,7 @@
       <c r="D5" s="28"/>
       <c r="E5" s="28"/>
       <c r="G5" s="27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H5" s="27"/>
       <c r="I5" s="28" t="str">
@@ -8304,7 +8323,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="27"/>
       <c r="C6" s="28" t="str">
@@ -8314,7 +8333,7 @@
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="G6" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H6" s="27"/>
       <c r="I6" s="28" t="str">
@@ -8327,7 +8346,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B7" s="27"/>
       <c r="C7" s="28" t="str">
@@ -8337,7 +8356,7 @@
       <c r="D7" s="28"/>
       <c r="E7" s="28"/>
       <c r="G7" s="27" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H7" s="27"/>
       <c r="I7" s="28" t="str">
@@ -8350,7 +8369,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="27"/>
       <c r="C8" s="28" t="str">
@@ -8362,7 +8381,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="27"/>
       <c r="C9" s="28" t="str">
@@ -8375,7 +8394,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B11" s="27"/>
       <c r="C11" s="28" t="str">
@@ -8385,7 +8404,7 @@
       <c r="D11" s="28"/>
       <c r="E11" s="28"/>
       <c r="G11" s="27" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H11" s="27"/>
       <c r="I11" s="57" t="n">
@@ -8397,7 +8416,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B12" s="27"/>
       <c r="C12" s="58" t="n">
@@ -8407,7 +8426,7 @@
       <c r="D12" s="58"/>
       <c r="E12" s="58"/>
       <c r="G12" s="27" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H12" s="27"/>
       <c r="I12" s="28" t="str">
@@ -8433,46 +8452,46 @@
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
       <c r="K13" s="32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L13" s="32"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K14" s="34" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L14" s="34" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8489,7 +8508,7 @@
         <v>רביעי</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E15" s="38" t="n">
         <f aca="false">IF(B15="","",הגדרות!$C$28)</f>
@@ -8537,7 +8556,7 @@
         <v>רביעי</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E16" s="38" t="n">
         <f aca="false">IF(B16="","",הגדרות!$C$28)</f>
@@ -8585,7 +8604,7 @@
         <v>רביעי</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E17" s="38" t="n">
         <f aca="false">IF(B17="","",הגדרות!$C$28)</f>
@@ -8633,7 +8652,7 @@
         <v>רביעי</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E18" s="38" t="n">
         <f aca="false">IF(B18="","",הגדרות!$C$28)</f>
@@ -8681,7 +8700,7 @@
         <v>רביעי</v>
       </c>
       <c r="D19" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E19" s="38" t="n">
         <f aca="false">IF(B19="","",הגדרות!$C$28)</f>
@@ -8729,7 +8748,7 @@
         <v/>
       </c>
       <c r="D20" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E20" s="38" t="str">
         <f aca="false">IF(B20="","",הגדרות!$C$28)</f>
@@ -8777,7 +8796,7 @@
         <v/>
       </c>
       <c r="D21" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E21" s="38" t="str">
         <f aca="false">IF(B21="","",הגדרות!$C$28)</f>
@@ -8825,7 +8844,7 @@
         <v/>
       </c>
       <c r="D22" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E22" s="38" t="str">
         <f aca="false">IF(B22="","",הגדרות!$C$28)</f>
@@ -8873,7 +8892,7 @@
         <v/>
       </c>
       <c r="D23" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E23" s="38" t="str">
         <f aca="false">IF(B23="","",הגדרות!$C$28)</f>
@@ -8921,7 +8940,7 @@
         <v/>
       </c>
       <c r="D24" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E24" s="38" t="str">
         <f aca="false">IF(B24="","",הגדרות!$C$28)</f>
@@ -8957,7 +8976,7 @@
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="45" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B25" s="45"/>
       <c r="C25" s="45"/>
@@ -8988,7 +9007,7 @@
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -9004,7 +9023,7 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
@@ -9059,7 +9078,7 @@
       <c r="F30" s="51"/>
       <c r="G30" s="51"/>
       <c r="H30" s="50" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I30" s="50"/>
       <c r="J30" s="50"/>
@@ -9081,7 +9100,7 @@
       <c r="F31" s="51"/>
       <c r="G31" s="51"/>
       <c r="H31" s="52" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I31" s="52"/>
       <c r="J31" s="52"/>
@@ -9126,7 +9145,7 @@
       <c r="F33" s="51"/>
       <c r="G33" s="51"/>
       <c r="H33" s="53" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I33" s="53"/>
       <c r="J33" s="53"/>
@@ -9150,7 +9169,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B35" s="49"/>
       <c r="C35" s="49"/>
@@ -9242,7 +9261,7 @@
       <c r="D42" s="55"/>
       <c r="E42" s="55"/>
       <c r="H42" s="55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I42" s="55"/>
       <c r="J42" s="55"/>
@@ -9250,6 +9269,7 @@
       <c r="L42" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="52">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
@@ -9360,147 +9380,147 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C4" s="14"/>
       <c r="F4" s="15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="16" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>34</v>
-      </c>
       <c r="F7" s="18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F10" s="18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C11" s="14"/>
       <c r="F11" s="18" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C16" s="14"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="16" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D19" s="19" t="n">
         <f aca="false">MATCH(C19,$F$5:$F$11,0)</f>
@@ -9509,7 +9529,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="19" t="n">
@@ -9519,7 +9539,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C21" s="20" t="n">
         <v>6</v>
@@ -9527,15 +9547,15 @@
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C23" s="21" t="n">
         <v>1000</v>
@@ -9543,7 +9563,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C24" s="21" t="n">
         <v>150</v>
@@ -9551,7 +9571,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C25" s="21" t="n">
         <v>150</v>
@@ -9559,7 +9579,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C26" s="22" t="n">
         <f aca="false">SUM(C23:C25)</f>
@@ -9568,7 +9588,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C27" s="21" t="n">
         <v>100</v>
@@ -9576,7 +9596,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C28" s="20" t="n">
         <v>6</v>
@@ -9584,7 +9604,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C29" s="20" t="n">
         <v>7</v>
@@ -9592,7 +9612,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="16" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C30" s="23" t="n">
         <v>1</v>
@@ -9600,7 +9620,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C31" s="23" t="n">
         <v>0.18</v>
@@ -9608,71 +9628,72 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C33" s="14"/>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="16" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C36" s="17"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C38" s="14"/>
     </row>
     <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <dataValidations count="1">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C19:C20" type="list">
       <formula1>$F$5:$F$11</formula1>
@@ -9712,7 +9733,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -9746,14 +9767,14 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
       <c r="G4" s="26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H4" s="26"/>
       <c r="I4" s="26"/>
@@ -9763,7 +9784,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="27"/>
       <c r="C5" s="28" t="str">
@@ -9773,7 +9794,7 @@
       <c r="D5" s="28"/>
       <c r="E5" s="28"/>
       <c r="G5" s="27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H5" s="27"/>
       <c r="I5" s="28" t="str">
@@ -9786,7 +9807,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="27"/>
       <c r="C6" s="28" t="str">
@@ -9796,7 +9817,7 @@
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="G6" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H6" s="27"/>
       <c r="I6" s="28" t="str">
@@ -9809,7 +9830,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B7" s="27"/>
       <c r="C7" s="28" t="str">
@@ -9819,7 +9840,7 @@
       <c r="D7" s="28"/>
       <c r="E7" s="28"/>
       <c r="G7" s="27" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H7" s="27"/>
       <c r="I7" s="28" t="str">
@@ -9832,7 +9853,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="27"/>
       <c r="C8" s="28" t="str">
@@ -9844,7 +9865,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="27"/>
       <c r="C9" s="28" t="str">
@@ -9857,20 +9878,20 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B11" s="27"/>
       <c r="C11" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D11" s="28"/>
       <c r="E11" s="28"/>
       <c r="G11" s="27" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H11" s="27"/>
       <c r="I11" s="29" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J11" s="29"/>
       <c r="K11" s="29"/>
@@ -9878,7 +9899,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B12" s="27"/>
       <c r="C12" s="30" t="n">
@@ -9887,7 +9908,7 @@
       <c r="D12" s="30"/>
       <c r="E12" s="30"/>
       <c r="G12" s="27" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H12" s="27"/>
       <c r="I12" s="28" t="str">
@@ -9913,46 +9934,46 @@
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
       <c r="K13" s="32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L13" s="32"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K14" s="34" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L14" s="34" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9968,7 +9989,7 @@
         <v>רביעי</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E15" s="38" t="n">
         <f aca="false">IF(B15="","",הגדרות!$C$28)</f>
@@ -10011,7 +10032,7 @@
         <v>שלישי</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E16" s="38" t="n">
         <f aca="false">IF(B16="","",הגדרות!$C$28)</f>
@@ -10054,7 +10075,7 @@
         <v>רביעי</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E17" s="38" t="n">
         <f aca="false">IF(B17="","",הגדרות!$C$28)</f>
@@ -10097,7 +10118,7 @@
         <v>שלישי</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E18" s="38" t="n">
         <f aca="false">IF(B18="","",הגדרות!$C$28)</f>
@@ -10140,7 +10161,7 @@
         <v>רביעי</v>
       </c>
       <c r="D19" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E19" s="38" t="n">
         <f aca="false">IF(B19="","",הגדרות!$C$28)</f>
@@ -10183,7 +10204,7 @@
         <v>שלישי</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E20" s="38" t="n">
         <f aca="false">IF(B20="","",הגדרות!$C$28)</f>
@@ -10226,7 +10247,7 @@
         <v>רביעי</v>
       </c>
       <c r="D21" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E21" s="38" t="n">
         <f aca="false">IF(B21="","",הגדרות!$C$28)</f>
@@ -10269,7 +10290,7 @@
         <v>שלישי</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E22" s="38" t="n">
         <f aca="false">IF(B22="","",הגדרות!$C$28)</f>
@@ -10312,7 +10333,7 @@
         <v>רביעי</v>
       </c>
       <c r="D23" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E23" s="38" t="n">
         <f aca="false">IF(B23="","",הגדרות!$C$28)</f>
@@ -10355,7 +10376,7 @@
         <v>שלישי</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E24" s="38" t="n">
         <f aca="false">IF(B24="","",הגדרות!$C$28)</f>
@@ -10398,7 +10419,7 @@
         <v>רביעי</v>
       </c>
       <c r="D25" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E25" s="38" t="n">
         <f aca="false">IF(B25="","",הגדרות!$C$28)</f>
@@ -10441,7 +10462,7 @@
         <v>שלישי</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E26" s="38" t="n">
         <f aca="false">IF(B26="","",הגדרות!$C$28)</f>
@@ -10484,7 +10505,7 @@
         <v>רביעי</v>
       </c>
       <c r="D27" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E27" s="38" t="n">
         <f aca="false">IF(B27="","",הגדרות!$C$28)</f>
@@ -10525,7 +10546,7 @@
         <v/>
       </c>
       <c r="D28" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E28" s="38" t="str">
         <f aca="false">IF(B28="","",הגדרות!$C$28)</f>
@@ -10566,7 +10587,7 @@
         <v/>
       </c>
       <c r="D29" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E29" s="38" t="str">
         <f aca="false">IF(B29="","",הגדרות!$C$28)</f>
@@ -10607,7 +10628,7 @@
         <v/>
       </c>
       <c r="D30" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E30" s="38" t="str">
         <f aca="false">IF(B30="","",הגדרות!$C$28)</f>
@@ -10648,7 +10669,7 @@
         <v/>
       </c>
       <c r="D31" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E31" s="38" t="str">
         <f aca="false">IF(B31="","",הגדרות!$C$28)</f>
@@ -10680,7 +10701,7 @@
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="45" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B32" s="45"/>
       <c r="C32" s="45"/>
@@ -10711,7 +10732,7 @@
     </row>
     <row r="33" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="48" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B33" s="48"/>
       <c r="C33" s="48"/>
@@ -10727,7 +10748,7 @@
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B35" s="49"/>
       <c r="C35" s="49"/>
@@ -10782,7 +10803,7 @@
       <c r="F37" s="51"/>
       <c r="G37" s="51"/>
       <c r="H37" s="50" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I37" s="50"/>
       <c r="J37" s="50"/>
@@ -10804,7 +10825,7 @@
       <c r="F38" s="51"/>
       <c r="G38" s="51"/>
       <c r="H38" s="52" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I38" s="52"/>
       <c r="J38" s="52"/>
@@ -10849,7 +10870,7 @@
       <c r="F40" s="51"/>
       <c r="G40" s="51"/>
       <c r="H40" s="53" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I40" s="53"/>
       <c r="J40" s="53"/>
@@ -10873,7 +10894,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B42" s="49"/>
       <c r="C42" s="49"/>
@@ -10965,7 +10986,7 @@
       <c r="D49" s="55"/>
       <c r="E49" s="55"/>
       <c r="H49" s="55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I49" s="55"/>
       <c r="J49" s="55"/>
@@ -10973,6 +10994,7 @@
       <c r="L49" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="52">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
@@ -11087,7 +11109,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -11129,14 +11151,14 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
       <c r="G4" s="26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H4" s="26"/>
       <c r="I4" s="26"/>
@@ -11146,7 +11168,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="27"/>
       <c r="C5" s="28" t="str">
@@ -11156,7 +11178,7 @@
       <c r="D5" s="28"/>
       <c r="E5" s="28"/>
       <c r="G5" s="27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H5" s="27"/>
       <c r="I5" s="28" t="str">
@@ -11169,7 +11191,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="27"/>
       <c r="C6" s="28" t="str">
@@ -11179,7 +11201,7 @@
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="G6" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H6" s="27"/>
       <c r="I6" s="28" t="str">
@@ -11192,7 +11214,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B7" s="27"/>
       <c r="C7" s="28" t="str">
@@ -11202,7 +11224,7 @@
       <c r="D7" s="28"/>
       <c r="E7" s="28"/>
       <c r="G7" s="27" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H7" s="27"/>
       <c r="I7" s="28" t="str">
@@ -11215,7 +11237,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="27"/>
       <c r="C8" s="28" t="str">
@@ -11227,7 +11249,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="27"/>
       <c r="C9" s="28" t="str">
@@ -11240,7 +11262,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B11" s="27"/>
       <c r="C11" s="28" t="str">
@@ -11250,7 +11272,7 @@
       <c r="D11" s="28"/>
       <c r="E11" s="28"/>
       <c r="G11" s="27" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H11" s="27"/>
       <c r="I11" s="57" t="n">
@@ -11262,7 +11284,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B12" s="27"/>
       <c r="C12" s="58" t="n">
@@ -11272,7 +11294,7 @@
       <c r="D12" s="58"/>
       <c r="E12" s="58"/>
       <c r="G12" s="27" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H12" s="27"/>
       <c r="I12" s="28" t="str">
@@ -11298,46 +11320,46 @@
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
       <c r="K13" s="32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L13" s="32"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K14" s="34" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L14" s="34" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11354,7 +11376,7 @@
         <v>רביעי</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E15" s="38" t="n">
         <f aca="false">IF(B15="","",הגדרות!$C$28)</f>
@@ -11402,7 +11424,7 @@
         <v>רביעי</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E16" s="38" t="n">
         <f aca="false">IF(B16="","",הגדרות!$C$28)</f>
@@ -11450,7 +11472,7 @@
         <v>רביעי</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E17" s="38" t="n">
         <f aca="false">IF(B17="","",הגדרות!$C$28)</f>
@@ -11498,7 +11520,7 @@
         <v>רביעי</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E18" s="38" t="n">
         <f aca="false">IF(B18="","",הגדרות!$C$28)</f>
@@ -11546,7 +11568,7 @@
         <v/>
       </c>
       <c r="D19" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E19" s="38" t="str">
         <f aca="false">IF(B19="","",הגדרות!$C$28)</f>
@@ -11594,7 +11616,7 @@
         <v/>
       </c>
       <c r="D20" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E20" s="38" t="str">
         <f aca="false">IF(B20="","",הגדרות!$C$28)</f>
@@ -11642,7 +11664,7 @@
         <v/>
       </c>
       <c r="D21" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E21" s="38" t="str">
         <f aca="false">IF(B21="","",הגדרות!$C$28)</f>
@@ -11690,7 +11712,7 @@
         <v/>
       </c>
       <c r="D22" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E22" s="38" t="str">
         <f aca="false">IF(B22="","",הגדרות!$C$28)</f>
@@ -11738,7 +11760,7 @@
         <v/>
       </c>
       <c r="D23" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E23" s="38" t="str">
         <f aca="false">IF(B23="","",הגדרות!$C$28)</f>
@@ -11786,7 +11808,7 @@
         <v/>
       </c>
       <c r="D24" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E24" s="38" t="str">
         <f aca="false">IF(B24="","",הגדרות!$C$28)</f>
@@ -11822,7 +11844,7 @@
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="45" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B25" s="45"/>
       <c r="C25" s="45"/>
@@ -11853,7 +11875,7 @@
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -11869,7 +11891,7 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
@@ -11924,7 +11946,7 @@
       <c r="F30" s="51"/>
       <c r="G30" s="51"/>
       <c r="H30" s="50" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I30" s="50"/>
       <c r="J30" s="50"/>
@@ -11946,7 +11968,7 @@
       <c r="F31" s="51"/>
       <c r="G31" s="51"/>
       <c r="H31" s="52" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I31" s="52"/>
       <c r="J31" s="52"/>
@@ -11991,7 +12013,7 @@
       <c r="F33" s="51"/>
       <c r="G33" s="51"/>
       <c r="H33" s="53" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I33" s="53"/>
       <c r="J33" s="53"/>
@@ -12015,7 +12037,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B35" s="49"/>
       <c r="C35" s="49"/>
@@ -12107,7 +12129,7 @@
       <c r="D42" s="55"/>
       <c r="E42" s="55"/>
       <c r="H42" s="55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I42" s="55"/>
       <c r="J42" s="55"/>
@@ -12115,6 +12137,7 @@
       <c r="L42" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="52">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
@@ -12229,7 +12252,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -12271,14 +12294,14 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
       <c r="G4" s="26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H4" s="26"/>
       <c r="I4" s="26"/>
@@ -12288,7 +12311,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="27"/>
       <c r="C5" s="28" t="str">
@@ -12298,7 +12321,7 @@
       <c r="D5" s="28"/>
       <c r="E5" s="28"/>
       <c r="G5" s="27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H5" s="27"/>
       <c r="I5" s="28" t="str">
@@ -12311,7 +12334,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="27"/>
       <c r="C6" s="28" t="str">
@@ -12321,7 +12344,7 @@
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="G6" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H6" s="27"/>
       <c r="I6" s="28" t="str">
@@ -12334,7 +12357,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B7" s="27"/>
       <c r="C7" s="28" t="str">
@@ -12344,7 +12367,7 @@
       <c r="D7" s="28"/>
       <c r="E7" s="28"/>
       <c r="G7" s="27" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H7" s="27"/>
       <c r="I7" s="28" t="str">
@@ -12357,7 +12380,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="27"/>
       <c r="C8" s="28" t="str">
@@ -12369,7 +12392,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="27"/>
       <c r="C9" s="28" t="str">
@@ -12382,7 +12405,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B11" s="27"/>
       <c r="C11" s="28" t="str">
@@ -12392,7 +12415,7 @@
       <c r="D11" s="28"/>
       <c r="E11" s="28"/>
       <c r="G11" s="27" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H11" s="27"/>
       <c r="I11" s="57" t="n">
@@ -12404,7 +12427,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B12" s="27"/>
       <c r="C12" s="58" t="n">
@@ -12414,7 +12437,7 @@
       <c r="D12" s="58"/>
       <c r="E12" s="58"/>
       <c r="G12" s="27" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H12" s="27"/>
       <c r="I12" s="28" t="str">
@@ -12440,46 +12463,46 @@
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
       <c r="K13" s="32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L13" s="32"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K14" s="34" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L14" s="34" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12496,7 +12519,7 @@
         <v>רביעי</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E15" s="38" t="n">
         <f aca="false">IF(B15="","",הגדרות!$C$28)</f>
@@ -12544,7 +12567,7 @@
         <v>רביעי</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E16" s="38" t="n">
         <f aca="false">IF(B16="","",הגדרות!$C$28)</f>
@@ -12592,7 +12615,7 @@
         <v>רביעי</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E17" s="38" t="n">
         <f aca="false">IF(B17="","",הגדרות!$C$28)</f>
@@ -12640,7 +12663,7 @@
         <v>רביעי</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E18" s="38" t="n">
         <f aca="false">IF(B18="","",הגדרות!$C$28)</f>
@@ -12688,7 +12711,7 @@
         <v/>
       </c>
       <c r="D19" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E19" s="38" t="str">
         <f aca="false">IF(B19="","",הגדרות!$C$28)</f>
@@ -12736,7 +12759,7 @@
         <v/>
       </c>
       <c r="D20" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E20" s="38" t="str">
         <f aca="false">IF(B20="","",הגדרות!$C$28)</f>
@@ -12784,7 +12807,7 @@
         <v/>
       </c>
       <c r="D21" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E21" s="38" t="str">
         <f aca="false">IF(B21="","",הגדרות!$C$28)</f>
@@ -12832,7 +12855,7 @@
         <v/>
       </c>
       <c r="D22" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E22" s="38" t="str">
         <f aca="false">IF(B22="","",הגדרות!$C$28)</f>
@@ -12880,7 +12903,7 @@
         <v/>
       </c>
       <c r="D23" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E23" s="38" t="str">
         <f aca="false">IF(B23="","",הגדרות!$C$28)</f>
@@ -12928,7 +12951,7 @@
         <v/>
       </c>
       <c r="D24" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E24" s="38" t="str">
         <f aca="false">IF(B24="","",הגדרות!$C$28)</f>
@@ -12964,7 +12987,7 @@
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="45" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B25" s="45"/>
       <c r="C25" s="45"/>
@@ -12995,7 +13018,7 @@
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -13011,7 +13034,7 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
@@ -13066,7 +13089,7 @@
       <c r="F30" s="51"/>
       <c r="G30" s="51"/>
       <c r="H30" s="50" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I30" s="50"/>
       <c r="J30" s="50"/>
@@ -13088,7 +13111,7 @@
       <c r="F31" s="51"/>
       <c r="G31" s="51"/>
       <c r="H31" s="52" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I31" s="52"/>
       <c r="J31" s="52"/>
@@ -13133,7 +13156,7 @@
       <c r="F33" s="51"/>
       <c r="G33" s="51"/>
       <c r="H33" s="53" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I33" s="53"/>
       <c r="J33" s="53"/>
@@ -13157,7 +13180,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B35" s="49"/>
       <c r="C35" s="49"/>
@@ -13249,7 +13272,7 @@
       <c r="D42" s="55"/>
       <c r="E42" s="55"/>
       <c r="H42" s="55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I42" s="55"/>
       <c r="J42" s="55"/>
@@ -13257,6 +13280,7 @@
       <c r="L42" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="52">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
@@ -13371,7 +13395,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -13413,14 +13437,14 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
       <c r="G4" s="26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H4" s="26"/>
       <c r="I4" s="26"/>
@@ -13430,7 +13454,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="27"/>
       <c r="C5" s="28" t="str">
@@ -13440,7 +13464,7 @@
       <c r="D5" s="28"/>
       <c r="E5" s="28"/>
       <c r="G5" s="27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H5" s="27"/>
       <c r="I5" s="28" t="str">
@@ -13453,7 +13477,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="27"/>
       <c r="C6" s="28" t="str">
@@ -13463,7 +13487,7 @@
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="G6" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H6" s="27"/>
       <c r="I6" s="28" t="str">
@@ -13476,7 +13500,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B7" s="27"/>
       <c r="C7" s="28" t="str">
@@ -13486,7 +13510,7 @@
       <c r="D7" s="28"/>
       <c r="E7" s="28"/>
       <c r="G7" s="27" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H7" s="27"/>
       <c r="I7" s="28" t="str">
@@ -13499,7 +13523,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="27"/>
       <c r="C8" s="28" t="str">
@@ -13511,7 +13535,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="27"/>
       <c r="C9" s="28" t="str">
@@ -13524,7 +13548,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B11" s="27"/>
       <c r="C11" s="28" t="str">
@@ -13534,7 +13558,7 @@
       <c r="D11" s="28"/>
       <c r="E11" s="28"/>
       <c r="G11" s="27" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H11" s="27"/>
       <c r="I11" s="57" t="n">
@@ -13546,7 +13570,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B12" s="27"/>
       <c r="C12" s="58" t="n">
@@ -13556,7 +13580,7 @@
       <c r="D12" s="58"/>
       <c r="E12" s="58"/>
       <c r="G12" s="27" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H12" s="27"/>
       <c r="I12" s="28" t="str">
@@ -13582,46 +13606,46 @@
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
       <c r="K13" s="32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L13" s="32"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K14" s="34" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L14" s="34" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13638,7 +13662,7 @@
         <v>רביעי</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E15" s="38" t="n">
         <f aca="false">IF(B15="","",הגדרות!$C$28)</f>
@@ -13686,7 +13710,7 @@
         <v>רביעי</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E16" s="38" t="n">
         <f aca="false">IF(B16="","",הגדרות!$C$28)</f>
@@ -13734,7 +13758,7 @@
         <v>רביעי</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E17" s="38" t="n">
         <f aca="false">IF(B17="","",הגדרות!$C$28)</f>
@@ -13782,7 +13806,7 @@
         <v>רביעי</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E18" s="38" t="n">
         <f aca="false">IF(B18="","",הגדרות!$C$28)</f>
@@ -13830,7 +13854,7 @@
         <v>רביעי</v>
       </c>
       <c r="D19" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E19" s="38" t="n">
         <f aca="false">IF(B19="","",הגדרות!$C$28)</f>
@@ -13878,7 +13902,7 @@
         <v/>
       </c>
       <c r="D20" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E20" s="38" t="str">
         <f aca="false">IF(B20="","",הגדרות!$C$28)</f>
@@ -13926,7 +13950,7 @@
         <v/>
       </c>
       <c r="D21" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E21" s="38" t="str">
         <f aca="false">IF(B21="","",הגדרות!$C$28)</f>
@@ -13974,7 +13998,7 @@
         <v/>
       </c>
       <c r="D22" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E22" s="38" t="str">
         <f aca="false">IF(B22="","",הגדרות!$C$28)</f>
@@ -14022,7 +14046,7 @@
         <v/>
       </c>
       <c r="D23" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E23" s="38" t="str">
         <f aca="false">IF(B23="","",הגדרות!$C$28)</f>
@@ -14070,7 +14094,7 @@
         <v/>
       </c>
       <c r="D24" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E24" s="38" t="str">
         <f aca="false">IF(B24="","",הגדרות!$C$28)</f>
@@ -14106,7 +14130,7 @@
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="45" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B25" s="45"/>
       <c r="C25" s="45"/>
@@ -14137,7 +14161,7 @@
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -14153,7 +14177,7 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
@@ -14208,7 +14232,7 @@
       <c r="F30" s="51"/>
       <c r="G30" s="51"/>
       <c r="H30" s="50" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I30" s="50"/>
       <c r="J30" s="50"/>
@@ -14230,7 +14254,7 @@
       <c r="F31" s="51"/>
       <c r="G31" s="51"/>
       <c r="H31" s="52" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I31" s="52"/>
       <c r="J31" s="52"/>
@@ -14275,7 +14299,7 @@
       <c r="F33" s="51"/>
       <c r="G33" s="51"/>
       <c r="H33" s="53" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I33" s="53"/>
       <c r="J33" s="53"/>
@@ -14299,7 +14323,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B35" s="49"/>
       <c r="C35" s="49"/>
@@ -14391,7 +14415,7 @@
       <c r="D42" s="55"/>
       <c r="E42" s="55"/>
       <c r="H42" s="55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I42" s="55"/>
       <c r="J42" s="55"/>
@@ -14399,6 +14423,7 @@
       <c r="L42" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="52">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
@@ -14513,7 +14538,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -14555,14 +14580,14 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
       <c r="G4" s="26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H4" s="26"/>
       <c r="I4" s="26"/>
@@ -14572,7 +14597,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="27"/>
       <c r="C5" s="28" t="str">
@@ -14582,7 +14607,7 @@
       <c r="D5" s="28"/>
       <c r="E5" s="28"/>
       <c r="G5" s="27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H5" s="27"/>
       <c r="I5" s="28" t="str">
@@ -14595,7 +14620,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="27"/>
       <c r="C6" s="28" t="str">
@@ -14605,7 +14630,7 @@
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="G6" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H6" s="27"/>
       <c r="I6" s="28" t="str">
@@ -14618,7 +14643,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B7" s="27"/>
       <c r="C7" s="28" t="str">
@@ -14628,7 +14653,7 @@
       <c r="D7" s="28"/>
       <c r="E7" s="28"/>
       <c r="G7" s="27" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H7" s="27"/>
       <c r="I7" s="28" t="str">
@@ -14641,7 +14666,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="27"/>
       <c r="C8" s="28" t="str">
@@ -14653,7 +14678,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="27"/>
       <c r="C9" s="28" t="str">
@@ -14666,7 +14691,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B11" s="27"/>
       <c r="C11" s="28" t="str">
@@ -14676,7 +14701,7 @@
       <c r="D11" s="28"/>
       <c r="E11" s="28"/>
       <c r="G11" s="27" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H11" s="27"/>
       <c r="I11" s="57" t="n">
@@ -14688,7 +14713,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B12" s="27"/>
       <c r="C12" s="58" t="n">
@@ -14698,7 +14723,7 @@
       <c r="D12" s="58"/>
       <c r="E12" s="58"/>
       <c r="G12" s="27" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H12" s="27"/>
       <c r="I12" s="28" t="str">
@@ -14724,46 +14749,46 @@
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
       <c r="K13" s="32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L13" s="32"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K14" s="34" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L14" s="34" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14780,7 +14805,7 @@
         <v>רביעי</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E15" s="38" t="n">
         <f aca="false">IF(B15="","",הגדרות!$C$28)</f>
@@ -14828,7 +14853,7 @@
         <v>רביעי</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E16" s="38" t="n">
         <f aca="false">IF(B16="","",הגדרות!$C$28)</f>
@@ -14876,7 +14901,7 @@
         <v>רביעי</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E17" s="38" t="n">
         <f aca="false">IF(B17="","",הגדרות!$C$28)</f>
@@ -14924,7 +14949,7 @@
         <v>רביעי</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E18" s="38" t="n">
         <f aca="false">IF(B18="","",הגדרות!$C$28)</f>
@@ -14972,7 +14997,7 @@
         <v/>
       </c>
       <c r="D19" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E19" s="38" t="str">
         <f aca="false">IF(B19="","",הגדרות!$C$28)</f>
@@ -15020,7 +15045,7 @@
         <v/>
       </c>
       <c r="D20" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E20" s="38" t="str">
         <f aca="false">IF(B20="","",הגדרות!$C$28)</f>
@@ -15068,7 +15093,7 @@
         <v/>
       </c>
       <c r="D21" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E21" s="38" t="str">
         <f aca="false">IF(B21="","",הגדרות!$C$28)</f>
@@ -15116,7 +15141,7 @@
         <v/>
       </c>
       <c r="D22" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E22" s="38" t="str">
         <f aca="false">IF(B22="","",הגדרות!$C$28)</f>
@@ -15164,7 +15189,7 @@
         <v/>
       </c>
       <c r="D23" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E23" s="38" t="str">
         <f aca="false">IF(B23="","",הגדרות!$C$28)</f>
@@ -15212,7 +15237,7 @@
         <v/>
       </c>
       <c r="D24" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E24" s="38" t="str">
         <f aca="false">IF(B24="","",הגדרות!$C$28)</f>
@@ -15248,7 +15273,7 @@
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="45" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B25" s="45"/>
       <c r="C25" s="45"/>
@@ -15279,7 +15304,7 @@
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -15295,7 +15320,7 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
@@ -15350,7 +15375,7 @@
       <c r="F30" s="51"/>
       <c r="G30" s="51"/>
       <c r="H30" s="50" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I30" s="50"/>
       <c r="J30" s="50"/>
@@ -15372,7 +15397,7 @@
       <c r="F31" s="51"/>
       <c r="G31" s="51"/>
       <c r="H31" s="52" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I31" s="52"/>
       <c r="J31" s="52"/>
@@ -15417,7 +15442,7 @@
       <c r="F33" s="51"/>
       <c r="G33" s="51"/>
       <c r="H33" s="53" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I33" s="53"/>
       <c r="J33" s="53"/>
@@ -15441,7 +15466,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B35" s="49"/>
       <c r="C35" s="49"/>
@@ -15533,7 +15558,7 @@
       <c r="D42" s="55"/>
       <c r="E42" s="55"/>
       <c r="H42" s="55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I42" s="55"/>
       <c r="J42" s="55"/>
@@ -15541,6 +15566,7 @@
       <c r="L42" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="52">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
@@ -15655,7 +15681,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -15697,14 +15723,14 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
       <c r="G4" s="26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H4" s="26"/>
       <c r="I4" s="26"/>
@@ -15714,7 +15740,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="27"/>
       <c r="C5" s="28" t="str">
@@ -15724,7 +15750,7 @@
       <c r="D5" s="28"/>
       <c r="E5" s="28"/>
       <c r="G5" s="27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H5" s="27"/>
       <c r="I5" s="28" t="str">
@@ -15737,7 +15763,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="27"/>
       <c r="C6" s="28" t="str">
@@ -15747,7 +15773,7 @@
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="G6" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H6" s="27"/>
       <c r="I6" s="28" t="str">
@@ -15760,7 +15786,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B7" s="27"/>
       <c r="C7" s="28" t="str">
@@ -15770,7 +15796,7 @@
       <c r="D7" s="28"/>
       <c r="E7" s="28"/>
       <c r="G7" s="27" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H7" s="27"/>
       <c r="I7" s="28" t="str">
@@ -15783,7 +15809,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="27"/>
       <c r="C8" s="28" t="str">
@@ -15795,7 +15821,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="27"/>
       <c r="C9" s="28" t="str">
@@ -15808,7 +15834,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B11" s="27"/>
       <c r="C11" s="28" t="str">
@@ -15818,7 +15844,7 @@
       <c r="D11" s="28"/>
       <c r="E11" s="28"/>
       <c r="G11" s="27" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H11" s="27"/>
       <c r="I11" s="57" t="n">
@@ -15830,7 +15856,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B12" s="27"/>
       <c r="C12" s="58" t="n">
@@ -15840,7 +15866,7 @@
       <c r="D12" s="58"/>
       <c r="E12" s="58"/>
       <c r="G12" s="27" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H12" s="27"/>
       <c r="I12" s="28" t="str">
@@ -15866,46 +15892,46 @@
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
       <c r="K13" s="32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L13" s="32"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K14" s="34" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L14" s="34" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15922,7 +15948,7 @@
         <v>רביעי</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E15" s="38" t="n">
         <f aca="false">IF(B15="","",הגדרות!$C$28)</f>
@@ -15970,7 +15996,7 @@
         <v>רביעי</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E16" s="38" t="n">
         <f aca="false">IF(B16="","",הגדרות!$C$28)</f>
@@ -16018,7 +16044,7 @@
         <v>רביעי</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E17" s="38" t="n">
         <f aca="false">IF(B17="","",הגדרות!$C$28)</f>
@@ -16066,7 +16092,7 @@
         <v>רביעי</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E18" s="38" t="n">
         <f aca="false">IF(B18="","",הגדרות!$C$28)</f>
@@ -16114,7 +16140,7 @@
         <v/>
       </c>
       <c r="D19" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E19" s="38" t="str">
         <f aca="false">IF(B19="","",הגדרות!$C$28)</f>
@@ -16162,7 +16188,7 @@
         <v/>
       </c>
       <c r="D20" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E20" s="38" t="str">
         <f aca="false">IF(B20="","",הגדרות!$C$28)</f>
@@ -16210,7 +16236,7 @@
         <v/>
       </c>
       <c r="D21" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E21" s="38" t="str">
         <f aca="false">IF(B21="","",הגדרות!$C$28)</f>
@@ -16258,7 +16284,7 @@
         <v/>
       </c>
       <c r="D22" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E22" s="38" t="str">
         <f aca="false">IF(B22="","",הגדרות!$C$28)</f>
@@ -16306,7 +16332,7 @@
         <v/>
       </c>
       <c r="D23" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E23" s="38" t="str">
         <f aca="false">IF(B23="","",הגדרות!$C$28)</f>
@@ -16354,7 +16380,7 @@
         <v/>
       </c>
       <c r="D24" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E24" s="38" t="str">
         <f aca="false">IF(B24="","",הגדרות!$C$28)</f>
@@ -16390,7 +16416,7 @@
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="45" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B25" s="45"/>
       <c r="C25" s="45"/>
@@ -16421,7 +16447,7 @@
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -16437,7 +16463,7 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
@@ -16492,7 +16518,7 @@
       <c r="F30" s="51"/>
       <c r="G30" s="51"/>
       <c r="H30" s="50" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I30" s="50"/>
       <c r="J30" s="50"/>
@@ -16514,7 +16540,7 @@
       <c r="F31" s="51"/>
       <c r="G31" s="51"/>
       <c r="H31" s="52" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I31" s="52"/>
       <c r="J31" s="52"/>
@@ -16559,7 +16585,7 @@
       <c r="F33" s="51"/>
       <c r="G33" s="51"/>
       <c r="H33" s="53" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I33" s="53"/>
       <c r="J33" s="53"/>
@@ -16583,7 +16609,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B35" s="49"/>
       <c r="C35" s="49"/>
@@ -16675,7 +16701,7 @@
       <c r="D42" s="55"/>
       <c r="E42" s="55"/>
       <c r="H42" s="55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I42" s="55"/>
       <c r="J42" s="55"/>
@@ -16683,6 +16709,7 @@
       <c r="L42" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="52">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
@@ -16797,7 +16824,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -16839,14 +16866,14 @@
     <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
       <c r="G4" s="26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H4" s="26"/>
       <c r="I4" s="26"/>
@@ -16856,7 +16883,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="27"/>
       <c r="C5" s="28" t="str">
@@ -16866,7 +16893,7 @@
       <c r="D5" s="28"/>
       <c r="E5" s="28"/>
       <c r="G5" s="27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H5" s="27"/>
       <c r="I5" s="28" t="str">
@@ -16879,7 +16906,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="27"/>
       <c r="C6" s="28" t="str">
@@ -16889,7 +16916,7 @@
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="G6" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H6" s="27"/>
       <c r="I6" s="28" t="str">
@@ -16902,7 +16929,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B7" s="27"/>
       <c r="C7" s="28" t="str">
@@ -16912,7 +16939,7 @@
       <c r="D7" s="28"/>
       <c r="E7" s="28"/>
       <c r="G7" s="27" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H7" s="27"/>
       <c r="I7" s="28" t="str">
@@ -16925,7 +16952,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="27"/>
       <c r="C8" s="28" t="str">
@@ -16937,7 +16964,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="27"/>
       <c r="C9" s="28" t="str">
@@ -16950,7 +16977,7 @@
     <row r="10" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B11" s="27"/>
       <c r="C11" s="28" t="str">
@@ -16960,7 +16987,7 @@
       <c r="D11" s="28"/>
       <c r="E11" s="28"/>
       <c r="G11" s="27" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H11" s="27"/>
       <c r="I11" s="57" t="n">
@@ -16972,7 +16999,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B12" s="27"/>
       <c r="C12" s="58" t="n">
@@ -16982,7 +17009,7 @@
       <c r="D12" s="58"/>
       <c r="E12" s="58"/>
       <c r="G12" s="27" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H12" s="27"/>
       <c r="I12" s="28" t="str">
@@ -17008,46 +17035,46 @@
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
       <c r="K13" s="32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L13" s="32"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K14" s="34" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L14" s="34" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17064,7 +17091,7 @@
         <v>רביעי</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E15" s="38" t="n">
         <f aca="false">IF(B15="","",הגדרות!$C$28)</f>
@@ -17112,7 +17139,7 @@
         <v>רביעי</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E16" s="38" t="n">
         <f aca="false">IF(B16="","",הגדרות!$C$28)</f>
@@ -17160,7 +17187,7 @@
         <v>רביעי</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E17" s="38" t="n">
         <f aca="false">IF(B17="","",הגדרות!$C$28)</f>
@@ -17208,7 +17235,7 @@
         <v>רביעי</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E18" s="38" t="n">
         <f aca="false">IF(B18="","",הגדרות!$C$28)</f>
@@ -17256,7 +17283,7 @@
         <v>רביעי</v>
       </c>
       <c r="D19" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E19" s="38" t="n">
         <f aca="false">IF(B19="","",הגדרות!$C$28)</f>
@@ -17304,7 +17331,7 @@
         <v/>
       </c>
       <c r="D20" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E20" s="38" t="str">
         <f aca="false">IF(B20="","",הגדרות!$C$28)</f>
@@ -17352,7 +17379,7 @@
         <v/>
       </c>
       <c r="D21" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E21" s="38" t="str">
         <f aca="false">IF(B21="","",הגדרות!$C$28)</f>
@@ -17400,7 +17427,7 @@
         <v/>
       </c>
       <c r="D22" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E22" s="38" t="str">
         <f aca="false">IF(B22="","",הגדרות!$C$28)</f>
@@ -17448,7 +17475,7 @@
         <v/>
       </c>
       <c r="D23" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E23" s="38" t="str">
         <f aca="false">IF(B23="","",הגדרות!$C$28)</f>
@@ -17496,7 +17523,7 @@
         <v/>
       </c>
       <c r="D24" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E24" s="38" t="str">
         <f aca="false">IF(B24="","",הגדרות!$C$28)</f>
@@ -17532,7 +17559,7 @@
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="45" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B25" s="45"/>
       <c r="C25" s="45"/>
@@ -17563,7 +17590,7 @@
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -17579,7 +17606,7 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
@@ -17634,7 +17661,7 @@
       <c r="F30" s="51"/>
       <c r="G30" s="51"/>
       <c r="H30" s="50" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I30" s="50"/>
       <c r="J30" s="50"/>
@@ -17656,7 +17683,7 @@
       <c r="F31" s="51"/>
       <c r="G31" s="51"/>
       <c r="H31" s="52" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I31" s="52"/>
       <c r="J31" s="52"/>
@@ -17701,7 +17728,7 @@
       <c r="F33" s="51"/>
       <c r="G33" s="51"/>
       <c r="H33" s="53" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I33" s="53"/>
       <c r="J33" s="53"/>
@@ -17725,7 +17752,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B35" s="49"/>
       <c r="C35" s="49"/>
@@ -17817,7 +17844,7 @@
       <c r="D42" s="55"/>
       <c r="E42" s="55"/>
       <c r="H42" s="55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I42" s="55"/>
       <c r="J42" s="55"/>
@@ -17825,6 +17852,7 @@
       <c r="L42" s="55"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true"/>
   <mergeCells count="52">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
